--- a/outputs/daily/hr_rankings_2026-08-24_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-24_full.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -4166,34 +4162,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6402,34 +6394,30 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10306,34 +10294,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21706,34 +21690,30 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -23102,34 +23082,30 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -32558,34 +32534,30 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -38138,34 +38110,30 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39266,34 +39234,30 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48780,34 +48744,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -52120,34 +52080,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
